--- a/artfynd/A 100-2023 artfynd.xlsx
+++ b/artfynd/A 100-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 100-2023 artfynd.xlsx
+++ b/artfynd/A 100-2023 artfynd.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 100-2023 artfynd.xlsx
+++ b/artfynd/A 100-2023 artfynd.xlsx
@@ -776,7 +776,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+          <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">

--- a/artfynd/A 100-2023 artfynd.xlsx
+++ b/artfynd/A 100-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>88691267</v>
+        <v>66401689</v>
       </c>
       <c r="B2" t="n">
-        <v>98620</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222541</v>
+        <v>219797</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Borsttåg</t>
+          <t>Purpurknipprot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Juncus squarrosus</t>
+          <t>Epipactis atrorubens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Brotorp norr om, Vg</t>
+          <t>Hållsdammen V, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>429596</v>
+        <v>429582</v>
       </c>
       <c r="R2" t="n">
-        <v>6473963</v>
+        <v>6474102</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,17 +752,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2017-06-25</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-23</t>
+          <t>2017-06-25</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Skogvägar, vandringsleder, vägdiken, kalhyggen, barrskog. Blandskog, kärr och mossar</t>
+          <t>Längs med Gröna milen</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,18 +775,470 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Vägkant, stigkant</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>87982442</v>
+      </c>
+      <c r="B3" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Hjälpadalen, Hållsdammen väst, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>429579</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6474097</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Våmb</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2011-06-30</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2011-06-30</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Barrskog, skogsvägar, mossar</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>119691128</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99093</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219797</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Purpurknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis atrorubens</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Hoffm.) Besser</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Hållsdammen väst, Vg</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>429582</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6474094</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Våmb</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Vid Motionsspår i skogskant</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66401698</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99803</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hållsdammen V, Vg</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>429593</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6474156</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Våmb</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-06-25</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-06-25</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Längs med Gröna milen</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Vägkant, stigkant</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kurt-Anders Johansson, Rolf-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Billingens flora</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>88691267</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99646</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222541</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Borsttåg</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Juncus squarrosus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Brotorp norr om, Vg</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>429596</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6473963</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skövde</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Våmb</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2020-08-23</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Skogvägar, vandringsleder, vägdiken, kalhyggen, barrskog. Blandskog, kärr och mossar</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Rolf-Göran Carlsson</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Rolf-Göran Carlsson, Kurt-Anders Johansson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY6" t="inlineStr">
         <is>
           <t>Billingens flora</t>
         </is>

--- a/artfynd/A 100-2023 artfynd.xlsx
+++ b/artfynd/A 100-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -796,6 +801,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66401689</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -902,6 +912,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87982442</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1025,6 +1040,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119691128</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1136,6 +1156,11 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66401698</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1243,8 +1268,20 @@
           <t>Billingens flora</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88691267</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>